--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1221,7 +1221,7 @@
 麻薬施用者免許番号の場合のsystemはFixed Valueの urn:oid:1.2.392.100495.20.3.32.1[都道府県番号] を使用する。  
 ( 頭に1をつけて末尾3桁で表現する。これは北海道などの場合、都道府県番号は01になるが、OIDでは先頭が0は許可されていないため、頭に1をつけて3桁で表現する)  
 つまり麻薬施用者免許番号を発行した都道府県ごとにsystemも異なる値となる。  
-医籍登録番号のsystemはFixed Valueの urn:oid:1.2.392.100495.20.3.31 を使用する。</t>
+医籍登録番号のsystemはFixed Valueの http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber を使用する。</t>
   </si>
   <si>
     <t xml:space="preserve">value:code}
@@ -1273,7 +1273,7 @@
     <t>【JP Core仕様】identifierには資格番号を入力する。  
 Codeは、v2 table 0360が例としてのっている。0360は、USER-DEFINED TABLES であるため、適切なCodeがなければ追加できる。  
 Periodにはその資格の開始日・終了日を入力する。（例：麻薬資格者の有効期限等の格納）  
-医籍登録番号　Practitioner.qualification.identifier　urn:oid:1.2.392.100495.20.3.31  
+医籍登録番号　Practitioner.qualification.identifier　http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber  
 麻薬施用者番号　Practitioner.qualification.identifier　urn:oid:1.2.392.100495.20.3.32.都道府県OID番号  
 　　（都道府県OID番号は、都道府県番号2桁の先頭に１をつけた3桁の番号）</t>
   </si>
@@ -1695,7 +1695,7 @@
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.31</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber</t>
   </si>
   <si>
     <t>Practitioner.qualification:medicalRegistrationNumber.identifier.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -314,16 +314,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -633,7 +633,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -653,7 +653,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>
@@ -671,7 +671,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「連絡先のための通信フォーム。」</t>
+    <t>連絡先のための通信フォーム。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -730,7 +730,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」(Setten no mokuteki wo tokutei suru.)</t>
+    <t>「接点の目的を特定する。」</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -744,7 +744,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」(Setten no shiyō.)</t>
+    <t>「接点の使用。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -769,10 +769,10 @@
 </t>
   </si>
   <si>
-    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
-  </si>
-  <si>
-    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -788,10 +788,10 @@
 </t>
   </si>
   <si>
-    <t>「コンタクトポイントが使用されている時間帯」</t>
-  </si>
-  <si>
-    <t>「接点が使用されていた/現在使用中である時間期間」</t>
+    <t>コンタクトポイントが使用されている時間帯</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1120,7 +1120,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>アドレスを歴史的な文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>Address.period</t>
@@ -1264,7 +1264,7 @@
     <t>Practitioner.qualification.identifier</t>
   </si>
   <si>
-    <t>開業医のこの資格の識別子 / An identifier for this qualification for the practitioner</t>
+    <t>開業医のこの資格のidentifier / An identifier for this qualification for the practitioner</t>
   </si>
   <si>
     <t>この人物のこの役割における資格に適用される識別子。</t>
@@ -1383,7 +1383,7 @@
     <t>都道府県別 麻薬施用者免許番号</t>
   </si>
   <si>
-    <t>この役割におけるこの人の資格に適用される識別子。 / An identifier that applies to this person's qualification in this role.</t>
+    <t>この役割におけるこの人の資格に適用されるidentifier。 / An identifier that applies to this person's qualification in this role.</t>
   </si>
   <si>
     <t>多くの場合、資格に特定のIDが割り当てられます。 / Often, specific identities are assigned for the qualification.</t>
@@ -1407,19 +1407,19 @@
     <t>Practitioner.qualification.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -1437,22 +1437,22 @@
     <t>Practitioner.qualification.identifier.type</t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -1527,7 +1527,7 @@
 　- urn:oid:1.2.392.100495.20.3.32.147(沖縄県)</t>
   </si>
   <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -1551,7 +1551,7 @@
     <t>都道府県別　麻薬施用者免許番号 【詳細参照】</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>都道府県別　麻薬施用者免許番号</t>
@@ -1575,7 +1575,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -1600,10 +1600,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -1686,13 +1686,13 @@
     <t>Practitioner.qualification:medicalRegistrationNumber.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber</t>
@@ -2076,7 +2076,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="60.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -633,7 +633,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -653,7 +653,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>
@@ -671,7 +671,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>連絡先のための通信フォーム。</t>
+    <t>「連絡先のための通信フォーム。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -769,10 +769,10 @@
 </t>
   </si>
   <si>
-    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
-  </si>
-  <si>
-    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
+    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
+  </si>
+  <si>
+    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -788,10 +788,10 @@
 </t>
   </si>
   <si>
-    <t>コンタクトポイントが使用されている時間帯</t>
-  </si>
-  <si>
-    <t>接点が使用されていた/現在使用中である時間期間</t>
+    <t>「コンタクトポイントが使用されている時間帯」</t>
+  </si>
+  <si>
+    <t>「接点が使用されていた/現在使用中である時間期間」</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -633,7 +633,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -653,7 +653,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>
@@ -671,7 +671,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「連絡先のための通信フォーム。」</t>
+    <t>連絡先のための通信フォーム。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -730,7 +730,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」</t>
+    <t>接点の目的を特定する。</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -744,7 +744,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」</t>
+    <t>接点の使用。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -769,10 +769,10 @@
 </t>
   </si>
   <si>
-    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
-  </si>
-  <si>
-    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -788,10 +788,10 @@
 </t>
   </si>
   <si>
-    <t>「コンタクトポイントが使用されている時間帯」</t>
-  </si>
-  <si>
-    <t>「接点が使用されていた/現在使用中である時間期間」</t>
+    <t>コンタクトポイントが使用されている時間帯</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -546,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
+    <t>開業医に関連付けられた名前 / The name(s) associated with the practitioner</t>
   </si>
   <si>
     <t>医療従事者の氏名（複数の場合もある）</t>
@@ -566,17 +566,13 @@
     <t>医療従事者が知られている名前。複数ある場合は、従事者が通常知られている名前を表示に使用する。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>ProviderName</t>
+    <t>XCN Components</t>
+  </si>
+  <si>
+    <t>./name</t>
+  </si>
+  <si>
+    <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
   </si>
   <si>
     <t>Practitioner.telecom</t>
@@ -2089,7 +2085,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="50.953125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3498,7 +3494,7 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>166</v>
@@ -3571,19 +3567,19 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3591,10 +3587,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3617,19 +3613,19 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3678,7 +3674,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3693,13 +3689,13 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3707,10 +3703,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3733,13 +3729,13 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3790,7 +3786,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3808,7 +3804,7 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3819,10 +3815,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3848,13 +3844,13 @@
         <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3892,19 +3888,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3916,13 +3912,13 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3933,10 +3929,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3962,13 +3958,13 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3994,31 +3990,31 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4027,19 +4023,19 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AJ17" t="s" s="2">
+      <c r="AK17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4047,10 +4043,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4073,19 +4069,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4134,7 +4130,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4146,16 +4142,16 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4163,10 +4159,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4192,16 +4188,16 @@
         <v>109</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4226,31 +4222,31 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z19" t="s" s="2">
+      <c r="AA19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4262,16 +4258,16 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4279,10 +4275,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4305,16 +4301,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4364,7 +4360,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4376,13 +4372,13 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4393,10 +4389,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4419,16 +4415,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4478,7 +4474,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4490,16 +4486,16 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4507,10 +4503,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4533,19 +4529,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4594,7 +4590,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4609,13 +4605,13 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4623,10 +4619,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4649,13 +4645,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4706,7 +4702,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4724,7 +4720,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4767,7 +4763,7 @@
         <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>138</v>
@@ -4808,19 +4804,19 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4838,7 +4834,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4849,10 +4845,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4878,16 +4874,16 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4912,31 +4908,31 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4951,13 +4947,13 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4965,10 +4961,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4994,13 +4990,13 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5026,31 +5022,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5065,10 +5061,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5079,10 +5075,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5105,19 +5101,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5166,7 +5162,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5181,10 +5177,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5195,10 +5191,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5221,16 +5217,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5280,7 +5276,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5295,13 +5291,13 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5309,14 +5305,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5335,16 +5331,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5394,7 +5390,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5409,13 +5405,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5423,14 +5419,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5449,16 +5445,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5508,7 +5504,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5523,10 +5519,10 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5537,14 +5533,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5563,16 +5559,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5622,7 +5618,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5637,13 +5633,13 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5651,14 +5647,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5677,16 +5673,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5736,7 +5732,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5751,13 +5747,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5765,10 +5761,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5791,16 +5787,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5850,7 +5846,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5865,13 +5861,13 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5879,10 +5875,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5905,19 +5901,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5966,7 +5962,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5981,13 +5977,13 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5995,10 +5991,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6024,14 +6020,14 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6056,14 +6052,14 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6080,7 +6076,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6095,13 +6091,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6109,10 +6105,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6135,17 +6131,17 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6194,7 +6190,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6209,13 +6205,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6223,10 +6219,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6249,19 +6245,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6310,7 +6306,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6328,10 +6324,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6339,10 +6335,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6365,16 +6361,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6412,17 +6408,17 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6437,13 +6433,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6451,10 +6447,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6477,13 +6473,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6534,7 +6530,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6552,7 +6548,7 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6563,10 +6559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6595,7 +6591,7 @@
         <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>138</v>
@@ -6648,7 +6644,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6666,7 +6662,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6677,14 +6673,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6706,10 +6702,10 @@
         <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>138</v>
@@ -6764,7 +6760,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6793,10 +6789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6822,16 +6818,16 @@
         <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6880,7 +6876,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6898,7 +6894,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6909,10 +6905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6935,16 +6931,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6970,14 +6966,14 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Y43" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Y43" t="s" s="2">
+      <c r="Z43" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6994,7 +6990,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -7012,10 +7008,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7023,10 +7019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7049,19 +7045,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7110,7 +7106,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7128,10 +7124,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7139,10 +7135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7165,16 +7161,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7224,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7242,7 +7238,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7253,13 +7249,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7269,25 +7265,25 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7338,7 +7334,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7353,13 +7349,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7367,10 +7363,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7393,13 +7389,13 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7450,7 +7446,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7468,7 +7464,7 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7479,10 +7475,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7511,7 +7507,7 @@
         <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>138</v>
@@ -7564,7 +7560,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7582,7 +7578,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7593,14 +7589,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7622,10 +7618,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -7680,7 +7676,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7709,10 +7705,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7738,14 +7734,14 @@
         <v>147</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7794,7 +7790,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7812,7 +7808,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7823,10 +7819,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7849,13 +7845,13 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7906,7 +7902,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7924,7 +7920,7 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7935,10 +7931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7967,7 +7963,7 @@
         <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>138</v>
@@ -8008,19 +8004,19 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8038,7 +8034,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8049,10 +8045,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8078,16 +8074,16 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8112,31 +8108,31 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8154,7 +8150,7 @@
         <v>132</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8165,10 +8161,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8191,19 +8187,19 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8228,31 +8224,31 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Y54" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="Z54" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="Z54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8267,10 +8263,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8281,10 +8277,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8310,16 +8306,16 @@
         <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8368,7 +8364,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8383,13 +8379,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8397,10 +8393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8423,16 +8419,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8482,7 +8478,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8497,13 +8493,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8511,10 +8507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8537,13 +8533,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8594,7 +8590,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8609,13 +8605,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8623,10 +8619,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8649,16 +8645,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8708,7 +8704,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8723,13 +8719,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8737,10 +8733,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8763,13 +8759,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="M59" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8781,7 +8777,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8796,11 +8792,11 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8818,7 +8814,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>89</v>
@@ -8836,10 +8832,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8847,10 +8843,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8873,17 +8869,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8932,7 +8928,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8950,10 +8946,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8961,10 +8957,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8987,13 +8983,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9044,7 +9040,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9062,7 +9058,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9073,13 +9069,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9101,13 +9097,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9158,7 +9154,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9173,13 +9169,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9187,10 +9183,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9213,13 +9209,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9270,7 +9266,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9288,7 +9284,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9299,10 +9295,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9331,7 +9327,7 @@
         <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>138</v>
@@ -9384,7 +9380,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9402,7 +9398,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9413,14 +9409,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9442,10 +9438,10 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -9500,7 +9496,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9529,10 +9525,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9558,14 +9554,14 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9614,7 +9610,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9632,7 +9628,7 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9643,10 +9639,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9669,13 +9665,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9726,7 +9722,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9744,7 +9740,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9755,10 +9751,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9787,7 +9783,7 @@
         <v>136</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>138</v>
@@ -9828,19 +9824,19 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9858,7 +9854,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9869,10 +9865,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9898,16 +9894,16 @@
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9932,31 +9928,31 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9974,7 +9970,7 @@
         <v>132</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9985,10 +9981,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10011,19 +10007,19 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10048,31 +10044,31 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Y70" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="Z70" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10087,10 +10083,10 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10101,10 +10097,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10130,23 +10126,23 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N71" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O71" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10188,7 +10184,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10203,13 +10199,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10217,10 +10213,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10243,16 +10239,16 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10302,7 +10298,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10317,13 +10313,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AM72" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10331,10 +10327,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10357,13 +10353,13 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10414,7 +10410,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10429,13 +10425,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL73" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="AM73" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10443,10 +10439,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10469,16 +10465,16 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10528,7 +10524,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10543,13 +10539,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10557,10 +10553,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10583,13 +10579,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="M75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10601,7 +10597,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -10616,11 +10612,11 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10638,7 +10634,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>89</v>
@@ -10656,10 +10652,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10667,10 +10663,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10693,17 +10689,17 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10752,7 +10748,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10770,10 +10766,10 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10781,10 +10777,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10807,13 +10803,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10864,7 +10860,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10882,7 +10878,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10893,10 +10889,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10919,19 +10915,19 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10980,7 +10976,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10995,13 +10991,13 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2865" uniqueCount="517">
   <si>
     <t>Property</t>
   </si>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -649,7 +649,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>
@@ -1377,12 +1377,6 @@
   </si>
   <si>
     <t>都道府県別 麻薬施用者免許番号</t>
-  </si>
-  <si>
-    <t>この役割におけるこの人の資格に適用されるidentifier。 / An identifier that applies to this person's qualification in this role.</t>
-  </si>
-  <si>
-    <t>多くの場合、資格に特定のIDが割り当てられます。 / Often, specific identities are assigned for the qualification.</t>
   </si>
   <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.identifier.id</t>
@@ -1617,9 +1611,6 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.code</t>
   </si>
   <si>
-    <t>資格のコード化された表現。 / Coded representation of the qualification.</t>
-  </si>
-  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicalLicenseCertificate_CS"/&gt;
@@ -1634,16 +1625,7 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.period</t>
   </si>
   <si>
-    <t>資格が有効な期間。 / Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>資格は多くの場合、限られた期間であり、取り消すことができます。 / Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.issuer</t>
-  </si>
-  <si>
-    <t>資格を規制および発行する組織。 / Organization that regulates and issues the qualification.</t>
   </si>
   <si>
     <t>Practitioner.qualification:medicalRegistrationNumber</t>
@@ -7737,11 +7719,13 @@
         <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7819,10 +7803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7931,10 +7915,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8045,10 +8029,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8074,16 +8058,16 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8111,28 +8095,28 @@
         <v>202</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8150,7 +8134,7 @@
         <v>132</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8161,10 +8145,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8190,16 +8174,16 @@
         <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8224,31 +8208,31 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8263,10 +8247,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8277,10 +8261,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8306,16 +8290,16 @@
         <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8364,7 +8348,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8379,13 +8363,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8393,10 +8377,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8422,13 +8406,13 @@
         <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8478,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8493,10 +8477,10 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>219</v>
@@ -8507,10 +8491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8536,10 +8520,10 @@
         <v>238</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8590,7 +8574,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8605,10 +8589,10 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>244</v>
@@ -8619,10 +8603,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8645,16 +8629,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8704,7 +8688,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8719,13 +8703,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8733,7 +8717,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>389</v>
@@ -8765,9 +8749,11 @@
         <v>391</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8777,7 +8763,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8796,7 +8782,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8843,7 +8829,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>398</v>
@@ -8875,11 +8861,13 @@
         <v>399</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>489</v>
+        <v>402</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8957,7 +8945,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>405</v>
@@ -8983,15 +8971,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9069,13 +9059,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>367</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9183,7 +9173,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>376</v>
@@ -9295,7 +9285,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>377</v>
@@ -9409,7 +9399,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>378</v>
@@ -9525,7 +9515,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>383</v>
@@ -9554,14 +9544,16 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9639,10 +9631,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9751,10 +9743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9865,10 +9857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9894,16 +9886,16 @@
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9931,28 +9923,28 @@
         <v>202</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9970,7 +9962,7 @@
         <v>132</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9981,10 +9973,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10010,16 +10002,16 @@
         <v>390</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10044,31 +10036,31 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10083,10 +10075,10 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10097,10 +10089,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10126,23 +10118,23 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10184,7 +10176,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10199,13 +10191,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10213,10 +10205,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10242,13 +10234,13 @@
         <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10298,7 +10290,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10313,10 +10305,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>219</v>
@@ -10327,10 +10319,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10356,10 +10348,10 @@
         <v>238</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10410,7 +10402,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10425,10 +10417,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>244</v>
@@ -10439,10 +10431,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10465,16 +10457,16 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10524,7 +10516,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10539,13 +10531,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10553,7 +10545,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>389</v>
@@ -10585,9 +10577,11 @@
         <v>391</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10597,7 +10591,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -10616,7 +10610,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10663,7 +10657,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>398</v>
@@ -10695,11 +10689,13 @@
         <v>399</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>489</v>
+        <v>402</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10777,7 +10773,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>405</v>
@@ -10803,15 +10799,17 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10889,10 +10887,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10918,16 +10916,16 @@
         <v>390</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10976,7 +10974,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10991,13 +10989,13 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -2030,17 +2030,17 @@
   <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.0546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.8671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.61328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.89453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="28.8203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2049,26 +2049,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.75390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1333,7 +1333,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1445,7 +1445,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1293,7 +1293,7 @@
     <t>資格のコード化された表現。</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および前後の調整を管理するための独自の構造を提供することが望ましい。</t>
+    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>example</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1220,7 +1220,7 @@
 医籍登録番号のsystemはFixed Valueの http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber を使用する。</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1220,7 +1220,7 @@
 医籍登録番号のsystemはFixed Valueの http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber を使用する。</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1293,7 +1293,7 @@
     <t>資格のコード化された表現。</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
+    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>example</t>
